--- a/_ForDRA/BVSimulationFiles/67.xlsx
+++ b/_ForDRA/BVSimulationFiles/67.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003184713375796178</v>
+        <v>0.006369426751592356</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003288635601743212</v>
+        <v>0.006577271203486424</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003392557827690245</v>
+        <v>0.006785115655380491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003496480053637278</v>
+        <v>0.006992960107274556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0003600402279584312</v>
+        <v>0.007200804559168624</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003704324505531344</v>
+        <v>0.007408649011062689</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003808246731478377</v>
+        <v>0.007616493462956754</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003912168957425411</v>
+        <v>0.007824337914850822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004016091183372444</v>
+        <v>0.008032182366744888</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004120013409319477</v>
+        <v>0.008240026818638954</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000422393563526651</v>
+        <v>0.008447871270533019</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004327857861213544</v>
+        <v>0.008655715722427088</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004431780087160576</v>
+        <v>0.008863560174321152</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000453570231310761</v>
+        <v>0.00907140462621522</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004639624539054643</v>
+        <v>0.009279249078109286</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004743546765001676</v>
+        <v>0.009487093530003352</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000484746899094871</v>
+        <v>0.00969493798189742</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004951391216895743</v>
+        <v>0.009902782433791488</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005055313442842777</v>
+        <v>0.01011062688568555</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005159235668789809</v>
+        <v>0.01031847133757962</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003184713375796178</v>
+        <v>0.006369426751592356</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003288635601743212</v>
+        <v>0.006577271203486424</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003392557827690245</v>
+        <v>0.006785115655380491</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003496480053637278</v>
+        <v>0.006992960107274556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003600402279584312</v>
+        <v>0.007200804559168624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003704324505531344</v>
+        <v>0.007408649011062689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003808246731478377</v>
+        <v>0.007616493462956754</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003912168957425411</v>
+        <v>0.007824337914850822</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004016091183372444</v>
+        <v>0.008032182366744888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004120013409319477</v>
+        <v>0.008240026818638954</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000422393563526651</v>
+        <v>0.008447871270533019</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004327857861213544</v>
+        <v>0.008655715722427088</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004431780087160576</v>
+        <v>0.008863560174321152</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000453570231310761</v>
+        <v>0.00907140462621522</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004639624539054643</v>
+        <v>0.009279249078109286</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004743546765001676</v>
+        <v>0.009487093530003352</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000484746899094871</v>
+        <v>0.00969493798189742</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004951391216895743</v>
+        <v>0.009902782433791488</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005055313442842777</v>
+        <v>0.01011062688568555</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005159235668789809</v>
+        <v>0.01031847133757962</v>
       </c>
     </row>
   </sheetData>
